--- a/data/trans_dic/P37A$medicoedad-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoedad-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,57</t>
+          <t>3,29; 8,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 12,09</t>
+          <t>4,92; 12,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,11</t>
+          <t>3,25; 8,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 17,7</t>
+          <t>11,09; 18,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,32</t>
+          <t>4,69; 10,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,28</t>
+          <t>4,95; 11,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,68</t>
+          <t>3,05; 8,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 23,14</t>
+          <t>15,14; 21,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,84</t>
+          <t>4,69; 8,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,76</t>
+          <t>5,68; 10,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,76</t>
+          <t>3,72; 7,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,02</t>
+          <t>14,03; 18,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,19</t>
+          <t>1,4; 4,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 11,25</t>
+          <t>5,88; 10,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,34</t>
+          <t>5,7; 10,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,48</t>
+          <t>7,65; 12,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,7</t>
+          <t>4,37; 8,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,2</t>
+          <t>7,77; 13,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,4</t>
+          <t>4,64; 9,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,72; 17,84</t>
+          <t>13,06; 17,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,08</t>
+          <t>3,35; 6,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,41</t>
+          <t>7,4; 11,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,03</t>
+          <t>5,91; 9,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,1</t>
+          <t>10,95; 14,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 10,85</t>
+          <t>4,61; 10,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 15,98</t>
+          <t>8,19; 15,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,74; 16,48</t>
+          <t>9,54; 16,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 21,05</t>
+          <t>14,27; 20,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 19,02</t>
+          <t>11,47; 19,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 17,31</t>
+          <t>9,77; 17,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 18,83</t>
+          <t>10,23; 18,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,66</t>
+          <t>13,43; 19,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,75</t>
+          <t>8,95; 13,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,98</t>
+          <t>10,11; 15,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,28</t>
+          <t>10,77; 16,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,38</t>
+          <t>14,56; 19,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,96</t>
+          <t>4,05; 9,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 12,34</t>
+          <t>6,3; 12,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,47</t>
+          <t>5,17; 10,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 19,65</t>
+          <t>10,97; 17,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 12,73</t>
+          <t>6,89; 13,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 15,45</t>
+          <t>8,67; 15,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 14,46</t>
+          <t>7,61; 14,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 15,27</t>
+          <t>11,93; 16,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 10,11</t>
+          <t>6,15; 9,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,68</t>
+          <t>8,2; 12,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 11,28</t>
+          <t>6,77; 11,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 15,74</t>
+          <t>12,19; 16,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,18</t>
+          <t>1,68; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 13,73</t>
+          <t>4,73; 12,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,41</t>
+          <t>3,08; 9,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,16</t>
+          <t>6,21; 12,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 13,24</t>
+          <t>4,95; 13,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 14,56</t>
+          <t>6,13; 14,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 13,9</t>
+          <t>5,66; 14,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 17,74</t>
+          <t>12,92; 19,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,67</t>
+          <t>4,33; 8,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,2</t>
+          <t>6,35; 12,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,15</t>
+          <t>5,24; 10,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,58</t>
+          <t>10,49; 14,5</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,92; 11,13</t>
+          <t>5,11; 11,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,14</t>
+          <t>8,5; 16,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,93; 18,2</t>
+          <t>10,12; 17,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,22; 23,28</t>
+          <t>16,63; 24,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,53; 16,61</t>
+          <t>8,67; 17,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,3</t>
+          <t>8,2; 15,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,07; 19,97</t>
+          <t>11,45; 20,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,74; 29,19</t>
+          <t>21,73; 29,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,78</t>
+          <t>7,54; 12,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,5</t>
+          <t>9,32; 14,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 17,74</t>
+          <t>11,4; 17,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,86; 25,22</t>
+          <t>20,2; 25,25</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,66</t>
+          <t>6,11; 10,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,15</t>
+          <t>6,28; 11,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 14,17</t>
+          <t>9,07; 14,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 13,79</t>
+          <t>9,52; 14,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,25</t>
+          <t>8,48; 13,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,17</t>
+          <t>6,32; 10,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 17,49</t>
+          <t>11,45; 16,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 66,87</t>
+          <t>10,81; 14,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,76; 10,91</t>
+          <t>7,82; 11,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,36</t>
+          <t>7,05; 10,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,17; 15,01</t>
+          <t>10,89; 14,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 50,66</t>
+          <t>10,86; 14,02</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,82</t>
+          <t>6,11; 9,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,72</t>
+          <t>7,36; 11,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,32</t>
+          <t>6,55; 10,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 14,27</t>
+          <t>10,54; 14,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 11,13</t>
+          <t>6,82; 11,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,33</t>
+          <t>8,93; 13,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,42</t>
+          <t>7,87; 12,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,2; 19,75</t>
+          <t>15,16; 19,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,96; 9,84</t>
+          <t>7,03; 9,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,85</t>
+          <t>8,71; 11,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,77</t>
+          <t>7,78; 10,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 16,06</t>
+          <t>13,62; 16,66</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,13</t>
+          <t>5,55; 7,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,19</t>
+          <t>8,09; 10,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,04</t>
+          <t>8,18; 10,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,52; 13,71</t>
+          <t>12,18; 14,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 10,77</t>
+          <t>8,7; 10,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,38; 11,44</t>
+          <t>9,4; 11,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,68; 11,97</t>
+          <t>9,63; 11,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,41; 34,86</t>
+          <t>15,25; 17,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,79</t>
+          <t>7,37; 8,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,53</t>
+          <t>9,1; 10,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9,22; 10,71</t>
+          <t>9,22; 10,72</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,62; 23,79</t>
+          <t>14,03; 15,4</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55638</t>
+          <t>57247</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98120</t>
+          <t>103275</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9051; 23409</t>
+          <t>8980; 23087</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15715; 35626</t>
+          <t>14488; 35446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10179; 23832</t>
+          <t>9559; 24494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32116; 55141</t>
+          <t>35365; 58156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11873; 29521</t>
+          <t>12239; 28565</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14258; 32411</t>
+          <t>14226; 32055</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9141; 25056</t>
+          <t>8816; 24537</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46943; 67010</t>
+          <t>47844; 67314</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25017; 47215</t>
+          <t>25024; 47546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33580; 62618</t>
+          <t>33048; 61855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21790; 45200</t>
+          <t>21642; 42686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84535; 114318</t>
+          <t>89103; 118343</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49006</t>
+          <t>52449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>83330</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>135779</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6842; 20645</t>
+          <t>6898; 20971</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30191; 56884</t>
+          <t>29705; 54604</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28730; 51983</t>
+          <t>28659; 52041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37998; 64687</t>
+          <t>40617; 68448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21049; 43840</t>
+          <t>22026; 44921</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39943; 69112</t>
+          <t>40701; 68393</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23464; 49180</t>
+          <t>24248; 49627</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65528; 91867</t>
+          <t>71364; 98008</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33889; 60575</t>
+          <t>33422; 60742</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77296; 117406</t>
+          <t>76150; 116622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57289; 92602</t>
+          <t>60618; 94124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>108367; 145665</t>
+          <t>117956; 156125</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55618</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57792</t>
+          <t>58546</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>113410</t>
+          <t>113481</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14933; 34595</t>
+          <t>14712; 32488</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27037; 51781</t>
+          <t>26523; 49840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31032; 52507</t>
+          <t>30377; 52776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45068; 66531</t>
+          <t>45095; 66277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38155; 63804</t>
+          <t>38484; 64332</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32955; 59043</t>
+          <t>33303; 59289</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35308; 63328</t>
+          <t>34397; 62933</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47715; 68638</t>
+          <t>47864; 68620</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58920; 89951</t>
+          <t>58553; 90354</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66103; 99594</t>
+          <t>67226; 100712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70650; 106640</t>
+          <t>70518; 106660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98100; 128925</t>
+          <t>97872; 128956</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46696</t>
+          <t>52214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>60198</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>103028</t>
+          <t>112412</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15137; 32141</t>
+          <t>14509; 33010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23038; 46147</t>
+          <t>23577; 46139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18751; 38719</t>
+          <t>19140; 37866</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36990; 61426</t>
+          <t>40929; 66342</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25649; 47289</t>
+          <t>25588; 48326</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34253; 60079</t>
+          <t>33735; 59101</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27884; 56006</t>
+          <t>29470; 57310</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30663; 72640</t>
+          <t>50344; 71188</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44441; 73841</t>
+          <t>44885; 72725</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62898; 96739</t>
+          <t>62537; 97561</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51882; 85395</t>
+          <t>51256; 84497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73863; 124089</t>
+          <t>96945; 127861</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>36305</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51786</t>
+          <t>54031</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3414; 12566</t>
+          <t>3419; 14198</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10001; 29194</t>
+          <t>10048; 27520</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6844; 19884</t>
+          <t>6499; 19062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11699; 23528</t>
+          <t>12778; 25028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11556; 27496</t>
+          <t>10285; 27014</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13585; 31971</t>
+          <t>13451; 32246</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12580; 30388</t>
+          <t>12369; 31644</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19213; 45905</t>
+          <t>29575; 43617</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16759; 35648</t>
+          <t>17810; 35316</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27874; 52736</t>
+          <t>27462; 52944</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21563; 43631</t>
+          <t>22502; 43779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35677; 63785</t>
+          <t>45569; 63018</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53141</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>65261</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>118402</t>
+          <t>120891</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13333; 30148</t>
+          <t>13849; 31154</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21849; 44211</t>
+          <t>23283; 44188</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26122; 47877</t>
+          <t>26621; 46464</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43740; 62785</t>
+          <t>45017; 65090</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23735; 46212</t>
+          <t>24127; 48405</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23765; 45650</t>
+          <t>22965; 44722</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30235; 54537</t>
+          <t>31265; 56101</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55885; 75026</t>
+          <t>57319; 76952</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42570; 70162</t>
+          <t>41369; 68786</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49929; 80356</t>
+          <t>51633; 81156</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61790; 95131</t>
+          <t>61140; 93225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>104580; 132852</t>
+          <t>107968; 134959</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69932</t>
+          <t>84499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>285012</t>
+          <t>97547</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>354945</t>
+          <t>182046</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37786; 65559</t>
+          <t>37571; 63313</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41646; 73887</t>
+          <t>41644; 73101</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59486; 93047</t>
+          <t>59534; 93517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56884; 86097</t>
+          <t>68487; 101826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>54876; 84534</t>
+          <t>54107; 85138</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45539; 77533</t>
+          <t>43865; 76016</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78863; 120875</t>
+          <t>79140; 117287</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>99691; 567869</t>
+          <t>83421; 115001</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>97309; 136696</t>
+          <t>97979; 139496</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94810; 140576</t>
+          <t>95582; 137443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150595; 202312</t>
+          <t>146736; 198628</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>165167; 746544</t>
+          <t>162066; 209205</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91368</t>
+          <t>101445</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>142691</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>215889</t>
+          <t>244136</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44471; 73044</t>
+          <t>45436; 73849</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57644; 91319</t>
+          <t>57314; 91459</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>50551; 80352</t>
+          <t>50997; 82193</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42644; 132505</t>
+          <t>84145; 117545</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53878; 87183</t>
+          <t>53427; 87704</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74063; 109788</t>
+          <t>73594; 109921</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>64960; 102615</t>
+          <t>64994; 103572</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>109106; 141739</t>
+          <t>126029; 161432</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106302; 150224</t>
+          <t>107345; 151469</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>137982; 189974</t>
+          <t>139665; 188039</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>124360; 172859</t>
+          <t>124831; 174457</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>131748; 264349</t>
+          <t>221858; 271398</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>425149</t>
+          <t>463037</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>758027</t>
+          <t>603015</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1183176</t>
+          <t>1066052</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>182065; 233678</t>
+          <t>181837; 233155</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>281299; 349296</t>
+          <t>277214; 352702</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>279868; 340765</t>
+          <t>277610; 344254</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>329445; 474346</t>
+          <t>430304; 497623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>296561; 363853</t>
+          <t>294153; 367029</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>333750; 407204</t>
+          <t>334380; 408830</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>343255; 424348</t>
+          <t>341239; 423050</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>572244; 1294196</t>
+          <t>570051; 638987</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>494405; 585031</t>
+          <t>490841; 585437</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>633556; 735181</t>
+          <t>635343; 741090</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>639898; 743353</t>
+          <t>639817; 743952</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>976840; 1706409</t>
+          <t>1019898; 1119506</t>
         </is>
       </c>
     </row>
